--- a/reports/一级子公司A_利润表_2026-02.xlsx
+++ b/reports/一级子公司A_利润表_2026-02.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>155548555</v>
+        <v>158278736</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>151573438</v>
+        <v>150812248</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>302485446</v>
+        <v>301677103</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>617875</v>
+        <v>618899</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1233610</v>
+        <v>1235414</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>534555</v>
+        <v>537514</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1068244</v>
+        <v>1073564</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>452174</v>
+        <v>455570</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>906119</v>
+        <v>910623</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>417420</v>
+        <v>418803</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>834954</v>
+        <v>837875</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>227024</v>
+        <v>227245</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>453141</v>
+        <v>455030</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>180954</v>
+        <v>181418</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>362101</v>
+        <v>363501</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>153118553</v>
+        <v>155839287</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>149143436</v>
+        <v>148372799</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>76596122</v>
+        <v>76275827</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>153162922</v>
+        <v>152897480</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1403019</v>
+        <v>1397363</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>2808619</v>
+        <v>2798467</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1269345</v>
+        <v>1262864</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>2541113</v>
+        <v>2525700</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>68355542</v>
+        <v>67909905</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>136082367</v>
+        <v>135547975</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1447367</v>
+        <v>1450617</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>2893408</v>
+        <v>2895184</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>632715</v>
+        <v>635411</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1269072</v>
+        <v>1268096</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2273752</v>
+        <v>2276162</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>4543598</v>
+        <v>4543368</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>998595</v>
+        <v>1001462</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>1992966</v>
+        <v>1999300</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>3888663</v>
+        <v>3917761</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>7785949</v>
+        <v>7825803</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>86454</v>
+        <v>93172</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>173219</v>
+        <v>186280</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2074796</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>4152183</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1380759</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>2765435</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>103830197</v>
+        <v>110734137</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>92759537</v>
+        <v>92177322</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>90859402</v>
+        <v>90283289</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>181281358</v>
+        <v>180924688</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1900135</v>
+        <v>1894033</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>3801609</v>
+        <v>3793897</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>3426289</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>6857154</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1097185</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>2193843</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>686773</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>1372030</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>825808</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>1648693</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>620725</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1238817</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>414643</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>827543</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>346029</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>690874</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1582190</v>
+        <v>1594539</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>3172114</v>
+        <v>3185896</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1225889</v>
+        <v>1229672</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>2451115</v>
+        <v>2459006</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>998818</v>
+        <v>1000876</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>1993258</v>
+        <v>2003149</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>7505436</v>
+        <v>7538268</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>15025921</v>
+        <v>15098877</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>335440</v>
+        <v>317242</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>672146</v>
+        <v>635739</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>648776</v>
+        <v>688438</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>1295204</v>
+        <v>1379858</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>733444</v>
+        <v>688438</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>1464737</v>
+        <v>1379858</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>86275</v>
+        <v>92231</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>172924</v>
+        <v>184724</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>350430</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>701246</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>600118</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1199803</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>234186</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>467806</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>176005</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>351364</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>293989</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>586718</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>864037</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>1724499</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>157307</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>314100</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>118039</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>235861</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>196647</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>393280</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>137477</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>275188</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>98011</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>196334</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>78237</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>156796</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>58555</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>117362</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>49288356</v>
+        <v>47313640</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>57144599</v>
+        <v>52991113</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>342663</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>685621</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>97439</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>194784</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>144180</v>
+        <v>154103</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>288978</v>
+        <v>307808</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>49144176</v>
+        <v>47502200</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5127353</v>
+        <v>5468631</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>10229399</v>
+        <v>10913710</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>44016823</v>
+        <v>42033569</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>44016823</v>
+        <v>42033569</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>44016823</v>
+        <v>42033569</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>44016823</v>
+        <v>42033569</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>44016823</v>
+        <v>42033569</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
